--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\620 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Sistema\WEB QR\info-toditico\energia-limpia\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17512648-3B96-4B6A-8E7B-DD4EF42D7EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E65B99-38BD-440E-839C-AB6BA6477045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -114,9 +114,6 @@
     <t>MICROPERFIL C34 A 150 BR. (SUSTITUYE AL C36)</t>
   </si>
   <si>
-    <t>PANEL SOLAR BIFACIAL 505W TRINA SOLAR</t>
-  </si>
-  <si>
     <t>TORNILLO AUTOTALADRANTE 5,5X25 + ARANDELA E16 CON EPDM</t>
   </si>
   <si>
@@ -163,6 +160,12 @@
   </si>
   <si>
     <t>TUBO CORRUGADO NEGRO 32MM (1 METRO)</t>
+  </si>
+  <si>
+    <t>SERVICIO DE CRIMPADO DE CONECTORES MC4</t>
+  </si>
+  <si>
+    <t>SERVICIO DE CONECCIÓN DEL CONECTOR XT60I AL CALBLE SOLAR</t>
   </si>
 </sst>
 </file>
@@ -521,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -542,7 +545,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="5">
         <v>0.04</v>
@@ -566,7 +569,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="5">
         <v>4</v>
@@ -606,7 +609,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5">
         <v>15</v>
@@ -622,7 +625,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5">
         <v>5</v>
@@ -638,7 +641,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="5">
         <v>250</v>
@@ -646,7 +649,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="5">
         <v>300</v>
@@ -654,7 +657,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="5">
         <v>452</v>
@@ -662,7 +665,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5">
         <v>500</v>
@@ -710,7 +713,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5">
         <v>80</v>
@@ -766,113 +769,121 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B32" s="5">
-        <v>169</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="7" t="s">
-        <v>33</v>
+      <c r="A33" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B33" s="5">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B34" s="5">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="6" t="s">
-        <v>22</v>
+      <c r="A35" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="B35" s="5">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="7" t="s">
-        <v>17</v>
+      <c r="A36" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="B36" s="5">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37" s="5">
-        <v>23</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="6" t="s">
-        <v>15</v>
+      <c r="A38" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B38" s="5">
-        <v>89</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B40" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="6" t="s">
+    <row r="42" spans="1:2">
+      <c r="A42" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B42" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="5">
+    <row r="43" spans="1:2">
+      <c r="A43" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="6" t="s">
+    <row r="44" spans="1:2">
+      <c r="A44" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B44" s="5">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="5">
-        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="7" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B45" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5">
         <v>2</v>
       </c>
     </row>
@@ -892,6 +903,9 @@
       <c r="A134" s="4"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B46">
+    <sortCondition ref="A3:A46"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Sistema\WEB QR\info-toditico\energia-limpia\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E65B99-38BD-440E-839C-AB6BA6477045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F40320-DDBC-4501-9009-078C270D278F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,7 +165,7 @@
     <t>SERVICIO DE CRIMPADO DE CONECTORES MC4</t>
   </si>
   <si>
-    <t>SERVICIO DE CONECCIÓN DEL CONECTOR XT60I AL CALBLE SOLAR</t>
+    <t>SERVICIO DE CONEXIÓN DEL CONECTOR XT60I AL CABLE SOLAR</t>
   </si>
 </sst>
 </file>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Sistema\WEB QR\info-toditico\energia-limpia\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F40320-DDBC-4501-9009-078C270D278F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C72986-090C-4FA4-8BEF-4F469C5B1CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -78,9 +78,6 @@
     <t>CRIMPADORA PARA TERMINALES MC4</t>
   </si>
   <si>
-    <t>PICA DE PUESTA A TIERRA 100µ - Ø 14,2 LONG 1,5 METROS</t>
-  </si>
-  <si>
     <t>CABLE TOPSOLAR PV H1Z272-K 1X6 1500 V -ROJO (1 metro)</t>
   </si>
   <si>
@@ -93,9 +90,6 @@
     <t xml:space="preserve">PERFIL C43 A 1800 Aluminio Bruto </t>
   </si>
   <si>
-    <t xml:space="preserve">PERFIL C43 A 2400 Aluminio Bruto </t>
-  </si>
-  <si>
     <t xml:space="preserve">TAPA PLÁSTICO PERFIL C43 </t>
   </si>
   <si>
@@ -121,9 +115,6 @@
   </si>
   <si>
     <t>PRECIO</t>
-  </si>
-  <si>
-    <t>PERFIL C43 A 1200 ANODIZADO</t>
   </si>
   <si>
     <t>TRIÁNGULO ABIERTO C43 A 1625</t>
@@ -524,7 +515,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -537,7 +528,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="5">
         <v>8</v>
@@ -545,7 +536,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5">
         <v>0.04</v>
@@ -569,7 +560,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="5">
         <v>4</v>
@@ -577,7 +568,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5">
         <v>4</v>
@@ -601,7 +592,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="5">
         <v>3.5</v>
@@ -609,7 +600,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5">
         <v>15</v>
@@ -617,7 +608,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5">
         <v>2</v>
@@ -625,7 +616,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B14" s="5">
         <v>5</v>
@@ -641,7 +632,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5">
         <v>250</v>
@@ -649,7 +640,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B17" s="5">
         <v>300</v>
@@ -657,7 +648,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B18" s="5">
         <v>452</v>
@@ -665,7 +656,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B19" s="5">
         <v>500</v>
@@ -713,7 +704,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5">
         <v>80</v>
@@ -737,7 +728,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5">
         <v>5</v>
@@ -745,7 +736,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B29" s="5">
         <v>4</v>
@@ -761,131 +752,119 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="7" t="s">
-        <v>32</v>
+      <c r="A32" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="B32" s="5">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B33" s="5">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B34" s="5">
-        <v>45</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="7" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="6" t="s">
-        <v>14</v>
+      <c r="A36" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B36" s="5">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="6" t="s">
-        <v>15</v>
+      <c r="A37" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="B37" s="5">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5">
-        <v>6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="7" t="s">
-        <v>46</v>
+      <c r="A39" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B39" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B40" s="5">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="7" t="s">
-        <v>40</v>
+      <c r="A41" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B41" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="6" t="s">
-        <v>23</v>
+      <c r="A42" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="B42" s="5">
-        <v>2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B44" s="5">
-        <v>0.2</v>
-      </c>
+      <c r="A44" s="7"/>
+      <c r="B44" s="5"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="5">
-        <v>70</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5">
-        <v>2</v>
-      </c>
+      <c r="A46" s="7"/>
+      <c r="B46" s="5"/>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="4"/>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Sistema\WEB QR\info-toditico\energia-limpia\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C72986-090C-4FA4-8BEF-4F469C5B1CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F67A14-0412-4D90-B6DF-ADC7D62FBF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>SERVICIO DE CONEXIÓN DEL CONECTOR XT60I AL CABLE SOLAR</t>
+  </si>
+  <si>
+    <t>BREAKER DC 20A</t>
   </si>
 </sst>
 </file>
@@ -536,39 +539,39 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5">
-        <v>0.04</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="B5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="6" t="s">
-        <v>3</v>
       </c>
       <c r="B6" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B7" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="B8" s="5">
         <v>4</v>
@@ -576,287 +579,291 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5">
         <v>4</v>
-      </c>
-      <c r="B9" s="5">
-        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5">
         <v>5</v>
       </c>
-      <c r="B10" s="5">
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="7" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B12" s="5">
         <v>3.5</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="6" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B14" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="7" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B15" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="6" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B16" s="5">
         <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="5">
-        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="5">
-        <v>452</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B20" s="5">
         <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="5">
-        <v>3.5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B25" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B26" s="5">
         <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="5">
-        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B28" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B29" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="7" t="s">
+    <row r="30" spans="1:2">
+      <c r="A30" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B30" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="6" t="s">
+    <row r="31" spans="1:2">
+      <c r="A31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B31" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="7" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B32" s="5">
         <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="5">
-        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B33" s="5">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B35" s="5">
         <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5">
-        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B39" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="6" t="s">
+    <row r="40" spans="1:2">
+      <c r="A40" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B40" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="7" t="s">
+    <row r="41" spans="1:2">
+      <c r="A41" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B41" s="5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="6" t="s">
+    <row r="42" spans="1:2">
+      <c r="A42" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B42" s="5">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="5">
-        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B44" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="7"/>
-      <c r="B44" s="5"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="6"/>
@@ -882,8 +889,8 @@
       <c r="A134" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B46">
-    <sortCondition ref="A3:A46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B44">
+    <sortCondition ref="A3:A44"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
